--- a/src/test/java/com/xpresso/qa/testdata/Xpresso_MTest_TestData.xlsx
+++ b/src/test/java/com/xpresso/qa/testdata/Xpresso_MTest_TestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rohit.mathur\RoinetGit\XpressoTestingGit\src\test\java\com\xpresso\qa\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F752F34-1A7B-4C7D-A51E-BC54AFDB438B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBDD6A76-B6B8-4D27-8525-27A5EF44573B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -117,9 +117,6 @@
     <t>CSPUserforGuarantor</t>
   </si>
   <si>
-    <t>CSP014006</t>
-  </si>
-  <si>
     <t>Admin Loan</t>
   </si>
   <si>
@@ -139,6 +136,9 @@
   </si>
   <si>
     <t>Agreement Fee</t>
+  </si>
+  <si>
+    <t>CSP187579</t>
   </si>
 </sst>
 </file>
@@ -483,6 +483,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B23"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="25.36328125" customWidth="1"/>
+    <col min="2" max="2" width="48.81640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
@@ -617,46 +621,46 @@
         <v>29</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" t="s">
         <v>31</v>
-      </c>
-      <c r="B18" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B20">
-        <v>50000</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
